--- a/Factura/Mapeo Factura.xlsx
+++ b/Factura/Mapeo Factura.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="43">
   <si>
     <t>Producto</t>
   </si>
@@ -150,6 +150,9 @@
   </si>
   <si>
     <t>cgarcia@gmail.com</t>
+  </si>
+  <si>
+    <t>PK, FK</t>
   </si>
 </sst>
 </file>
@@ -234,7 +237,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -245,6 +248,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -563,10 +567,10 @@
         <v>38</v>
       </c>
       <c r="H3" t="s">
-        <v>1</v>
+        <v>42</v>
       </c>
       <c r="I3" t="s">
-        <v>1</v>
+        <v>42</v>
       </c>
       <c r="M3" t="s">
         <v>1</v>
@@ -768,12 +772,24 @@
       </c>
     </row>
     <row r="7" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A7" s="2"/>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-      <c r="F7" s="3"/>
+      <c r="A7" s="2">
+        <v>1003</v>
+      </c>
+      <c r="B7" s="6">
+        <v>46037</v>
+      </c>
+      <c r="C7" s="2">
+        <v>1111</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E7" s="2">
+        <v>80</v>
+      </c>
+      <c r="F7" s="10">
+        <v>1111</v>
+      </c>
       <c r="G7" s="4"/>
       <c r="H7" s="2">
         <v>1001</v>
@@ -815,7 +831,7 @@
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
+      <c r="E8" s="3"/>
       <c r="F8" s="2"/>
       <c r="G8" s="4"/>
       <c r="H8" s="2">
@@ -861,10 +877,18 @@
       <c r="E9" s="2"/>
       <c r="F9" s="2"/>
       <c r="G9" s="4"/>
-      <c r="H9" s="2"/>
-      <c r="I9" s="2"/>
-      <c r="J9" s="2"/>
-      <c r="K9" s="2"/>
+      <c r="H9" s="2">
+        <v>1003</v>
+      </c>
+      <c r="I9" s="2">
+        <v>101</v>
+      </c>
+      <c r="J9" s="2">
+        <v>20</v>
+      </c>
+      <c r="K9" s="2">
+        <v>2</v>
+      </c>
       <c r="M9" s="2">
         <v>104</v>
       </c>
@@ -896,10 +920,18 @@
       <c r="E10" s="2"/>
       <c r="F10" s="2"/>
       <c r="G10" s="4"/>
-      <c r="H10" s="2"/>
-      <c r="I10" s="2"/>
-      <c r="J10" s="2"/>
-      <c r="K10" s="2"/>
+      <c r="H10" s="2">
+        <v>1003</v>
+      </c>
+      <c r="I10" s="2">
+        <v>107</v>
+      </c>
+      <c r="J10" s="2">
+        <v>40</v>
+      </c>
+      <c r="K10" s="2">
+        <v>1</v>
+      </c>
       <c r="M10" s="2">
         <v>105</v>
       </c>
